--- a/db/templates/incoming_invoice_default.xlsx
+++ b/db/templates/incoming_invoice_default.xlsx
@@ -29,7 +29,7 @@
     <t>{{vendor.postalCode}} {{vendor.city}}</t>
   </si>
   <si>
-    <t>VAT: {{vendor.vatin}}</t>
+    <t>Matricule fiscal: {{vendor.vatin}}</t>
   </si>
   <si>
     <t>{{vendor.email}} | {{vendor.phone}}</t>
@@ -65,7 +65,7 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>VAT: {{organization.vatin}}</t>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
   </si>
   <si>
     <t>Description</t>

--- a/db/templates/incoming_invoice_default.xlsx
+++ b/db/templates/incoming_invoice_default.xlsx
@@ -7,18 +7,36 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Incoming Invoice" sheetId="1" r:id="rId1"/>
+    <sheet name="Facture fournisseur" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Incoming Invoice'!$1:$13</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Facture fournisseur'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+  <si>
+    <t>{{organization.logo}}</t>
+  </si>
+  <si>
+    <t>{{organization.name}}</t>
+  </si>
+  <si>
+    <t>{{organization.street}} {{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}} {{organization.city}}</t>
+  </si>
+  <si>
+    <t>Tél : {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>MF : {{organization.vatin}}</t>
+  </si>
   <si>
     <t>{{vendor.name}}</t>
   </si>
@@ -29,274 +47,304 @@
     <t>{{vendor.postalCode}} {{vendor.city}}</t>
   </si>
   <si>
-    <t>Matricule fiscal: {{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>{{vendor.email}} | {{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>INCOMING INVOICE</t>
-  </si>
-  <si>
-    <t>Vendor invoice number: {{incomingInvoice.number}}</t>
-  </si>
-  <si>
-    <t>Date: {{incomingInvoice.date}}</t>
-  </si>
-  <si>
-    <t>Due date: {{incomingInvoice.dueDate}}</t>
-  </si>
-  <si>
-    <t>Reference: {{incomingInvoice.reference}}</t>
-  </si>
-  <si>
-    <t>Purchase order: {{incomingInvoice.purchaseOrder}}</t>
-  </si>
-  <si>
-    <t>Billed To</t>
-  </si>
-  <si>
-    <t>{{organization.name}}</t>
-  </si>
-  <si>
-    <t>{{organization.street}} {{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}} {{organization.city}}</t>
-  </si>
-  <si>
-    <t>Matricule fiscal: {{organization.vatin}}</t>
+    <t>Tel: {{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>MF: {{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>Facture N°: {{incomingInvoice.number}}</t>
+  </si>
+  <si>
+    <t>Date : {{incomingInvoice.date}}</t>
+  </si>
+  <si>
+    <t>Désignation</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>P.U HT</t>
+  </si>
+  <si>
+    <t>TOTAL HT</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Taux TVA %</t>
+  </si>
+  <si>
+    <t>Base TVA</t>
+  </si>
+  <si>
+    <t>Montant TVA</t>
+  </si>
+  <si>
+    <t>{{taxLines.rate}}</t>
+  </si>
+  <si>
+    <t>{{taxLines.base}}</t>
+  </si>
+  <si>
+    <t>{{taxLines.amount}}</t>
+  </si>
+  <si>
+    <t>{{#taxLines}}</t>
+  </si>
+  <si>
+    <t>Total Brut HTVA</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.subTotal}}</t>
+  </si>
+  <si>
+    <t>Total TVA</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.taxTotal}}</t>
+  </si>
+  <si>
+    <t>Total TTC</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.total}}</t>
+  </si>
+  <si>
+    <t>Cachet et Signature</t>
+  </si>
+  <si>
+    <t>IBAN : {{organization.iban}}</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Buyer logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.number}}</t>
+  </si>
+  <si>
+    <t>Vendor's invoice number</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.date}}</t>
+  </si>
+  <si>
+    <t>Bill date</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Payment due date, blank if unset</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.reference}}</t>
+  </si>
+  <si>
+    <t>Free-text reference, blank if unset</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.purchaseOrder}}</t>
+  </si>
+  <si>
+    <t>Linked purchase order number, blank if unset</t>
+  </si>
+  <si>
+    <t>Buyer (bill recipient) company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Buyer VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Buyer email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Buyer phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Buyer website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Buyer street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Buyer house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Buyer postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Buyer city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Buyer IBAN</t>
+  </si>
+  <si>
+    <t>Buyer bank name</t>
+  </si>
+  <si>
+    <t>Vendor name</t>
+  </si>
+  <si>
+    <t>{{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>Vendor VAT number</t>
+  </si>
+  <si>
+    <t>{{vendor.email}}</t>
+  </si>
+  <si>
+    <t>Vendor email</t>
+  </si>
+  <si>
+    <t>{{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>Vendor phone</t>
+  </si>
+  <si>
+    <t>{{vendor.street}}</t>
+  </si>
+  <si>
+    <t>Vendor street</t>
+  </si>
+  <si>
+    <t>{{vendor.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Vendor house number</t>
+  </si>
+  <si>
+    <t>{{vendor.postalCode}}</t>
+  </si>
+  <si>
+    <t>Vendor postal code</t>
+  </si>
+  <si>
+    <t>{{vendor.city}}</t>
+  </si>
+  <si>
+    <t>Vendor city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Line item description</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Tax Rate</t>
-  </si>
-  <si>
-    <t>Line Total</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
+    <t>Unit price, formatted with currency</t>
   </si>
   <si>
     <t>{{lineItems.taxRate}}</t>
   </si>
   <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.subTotal}}</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.taxTotal}}</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.total}}</t>
-  </si>
-  <si>
-    <t>Notes: {{incomingInvoice.notes}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.number}}</t>
-  </si>
-  <si>
-    <t>Vendor's own invoice number</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.date}}</t>
-  </si>
-  <si>
-    <t>Invoice date</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.dueDate}}</t>
-  </si>
-  <si>
-    <t>Payment due date, blank if unset</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.reference}}</t>
-  </si>
-  <si>
-    <t>Free-text reference, blank if unset</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.purchaseOrder}}</t>
-  </si>
-  <si>
-    <t>Linked purchase order number, blank if unlinked</t>
-  </si>
-  <si>
-    <t>Vendor company name</t>
-  </si>
-  <si>
-    <t>{{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>Vendor VAT number</t>
-  </si>
-  <si>
-    <t>{{vendor.email}}</t>
-  </si>
-  <si>
-    <t>Vendor email</t>
-  </si>
-  <si>
-    <t>{{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>Vendor phone</t>
-  </si>
-  <si>
-    <t>{{vendor.street}}</t>
-  </si>
-  <si>
-    <t>Vendor street</t>
-  </si>
-  <si>
-    <t>{{vendor.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Vendor house number</t>
-  </si>
-  <si>
-    <t>{{vendor.postalCode}}</t>
-  </si>
-  <si>
-    <t>Vendor postal code</t>
-  </si>
-  <si>
-    <t>{{vendor.city}}</t>
-  </si>
-  <si>
-    <t>Vendor city</t>
-  </si>
-  <si>
-    <t>Buyer (your own) company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Buyer VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Buyer email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Buyer phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Buyer website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Buyer street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Buyer house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Buyer postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Buyer city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
-    <t>Unit price, formatted with currency</t>
-  </si>
-  <si>
     <t>Tax rate percentage (e.g. 19.5%), blank if unset</t>
   </si>
   <si>
     <t>Quantity x unit price, formatted with currency</t>
   </si>
   <si>
+    <t>VAT recap</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per distinct tax rate</t>
+  </si>
+  <si>
+    <t>Tax rate percentage (e.g. 19%)</t>
+  </si>
+  <si>
+    <t>Taxable base for this rate</t>
+  </si>
+  <si>
+    <t>VAT amount for this rate</t>
+  </si>
+  <si>
     <t>Footer</t>
   </si>
   <si>
-    <t>Subtotal before tax</t>
-  </si>
-  <si>
-    <t>Total tax</t>
-  </si>
-  <si>
-    <t>Grand total</t>
+    <t>Subtotal before tax (stored, server-validated)</t>
+  </si>
+  <si>
+    <t>Total tax (stored, server-validated)</t>
+  </si>
+  <si>
+    <t>Grand total (stored, server-validated)</t>
   </si>
   <si>
     <t>{{incomingInvoice.notes}}</t>
@@ -311,7 +359,7 @@
     <t>{{export.generatedDate}}</t>
   </si>
   <si>
-    <t>Date this file was exported (not the invoice's own date), in the organization's date format</t>
+    <t>Date this file was exported, in the organization's date format</t>
   </si>
   <si>
     <t>{{export.generatedTime}}</t>
@@ -323,14 +371,14 @@
     <t>&amp;P (page number) / &amp;N (total pages)</t>
   </si>
   <si>
-    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
+    <t>Native Excel/LibreOffice codes, only work in Page Layout ▸ Header/Footer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -351,13 +399,19 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="12"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
       <color/>
       <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
@@ -374,16 +428,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -391,11 +445,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -403,22 +471,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -694,152 +774,194 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="1" width="28"/>
-    <col customWidth="true" max="5" min="3" width="14"/>
-    <col customWidth="true" max="6" min="6" width="16"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="34"/>
+    <col customWidth="true" max="4" min="3" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
+      <c r="J12" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G14" t="s">
+      <c r="B16" s="7" t="s">
         <v>26</v>
       </c>
+      <c r="C16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="17">
-      <c r="E17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="E18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="E19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
+      <c r="D17" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="F17" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
+  <mergeCells count="10">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:G28"/>
   </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -859,341 +981,403 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>34</v>
+      <c r="A1" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>35</v>
+      <c r="A2" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
+      <c r="A4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>38</v>
+      <c r="A5" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="s">
-        <v>83</v>
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
+      <c r="A32" s="11" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="s">
-        <v>89</v>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
+      <c r="A39" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="s">
-        <v>95</v>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" t="s">
-        <v>101</v>
+      <c r="A44" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A49:C49"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/incoming_invoice_default.xlsx
+++ b/db/templates/incoming_invoice_default.xlsx
@@ -7,329 +7,326 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Facture fournisseur" sheetId="1" r:id="rId1"/>
+    <sheet name="Incoming Invoice" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Facture fournisseur'!$1:$11</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Incoming Invoice'!$1:$13</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+  <si>
+    <t>{{vendor.name}}</t>
+  </si>
+  <si>
+    <t>{{vendor.street}} {{vendor.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{vendor.postalCode}} {{vendor.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>{{vendor.email}} | {{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>INCOMING INVOICE</t>
+  </si>
+  <si>
+    <t>Vendor invoice number: {{incomingInvoice.number}}</t>
+  </si>
+  <si>
+    <t>Date: {{incomingInvoice.date}}</t>
+  </si>
+  <si>
+    <t>Due date: {{incomingInvoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Reference: {{incomingInvoice.reference}}</t>
+  </si>
+  <si>
+    <t>Purchase order: {{incomingInvoice.purchaseOrder}}</t>
+  </si>
+  <si>
+    <t>Billed To</t>
+  </si>
+  <si>
+    <t>{{organization.name}}</t>
+  </si>
+  <si>
+    <t>{{organization.street}} {{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}} {{organization.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Line Total</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.taxRate}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.subTotal}}</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.taxTotal}}</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.total}}</t>
+  </si>
+  <si>
+    <t>Notes: {{incomingInvoice.notes}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
   <si>
     <t>{{organization.logo}}</t>
   </si>
   <si>
-    <t>{{organization.name}}</t>
-  </si>
-  <si>
-    <t>{{organization.street}} {{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}} {{organization.city}}</t>
-  </si>
-  <si>
-    <t>Tél : {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>MF : {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{vendor.name}}</t>
-  </si>
-  <si>
-    <t>{{vendor.street}} {{vendor.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{vendor.postalCode}} {{vendor.city}}</t>
-  </si>
-  <si>
-    <t>Tel: {{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>MF: {{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>Facture N°: {{incomingInvoice.number}}</t>
-  </si>
-  <si>
-    <t>Date : {{incomingInvoice.date}}</t>
-  </si>
-  <si>
-    <t>Désignation</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
-    <t>P.U HT</t>
-  </si>
-  <si>
-    <t>TOTAL HT</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Taux TVA %</t>
-  </si>
-  <si>
-    <t>Base TVA</t>
-  </si>
-  <si>
-    <t>Montant TVA</t>
+    <t>Buyer logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.number}}</t>
+  </si>
+  <si>
+    <t>Vendor's invoice number</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.date}}</t>
+  </si>
+  <si>
+    <t>Bill date</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Payment due date, blank if unset</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.reference}}</t>
+  </si>
+  <si>
+    <t>Free-text reference, blank if unset</t>
+  </si>
+  <si>
+    <t>{{incomingInvoice.purchaseOrder}}</t>
+  </si>
+  <si>
+    <t>Linked purchase order number, blank if unset</t>
+  </si>
+  <si>
+    <t>Buyer (bill recipient) company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Buyer VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Buyer email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Buyer phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Buyer website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Buyer street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Buyer house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Buyer postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Buyer city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Buyer IBAN</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Buyer bank name</t>
+  </si>
+  <si>
+    <t>Vendor name</t>
+  </si>
+  <si>
+    <t>{{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>Vendor VAT number</t>
+  </si>
+  <si>
+    <t>{{vendor.email}}</t>
+  </si>
+  <si>
+    <t>Vendor email</t>
+  </si>
+  <si>
+    <t>{{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>Vendor phone</t>
+  </si>
+  <si>
+    <t>{{vendor.street}}</t>
+  </si>
+  <si>
+    <t>Vendor street</t>
+  </si>
+  <si>
+    <t>{{vendor.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Vendor house number</t>
+  </si>
+  <si>
+    <t>{{vendor.postalCode}}</t>
+  </si>
+  <si>
+    <t>Vendor postal code</t>
+  </si>
+  <si>
+    <t>{{vendor.city}}</t>
+  </si>
+  <si>
+    <t>Vendor city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Line item description</t>
+  </si>
+  <si>
+    <t>Unit price, formatted with currency</t>
+  </si>
+  <si>
+    <t>Tax rate percentage (e.g. 19.5%), blank if unset</t>
+  </si>
+  <si>
+    <t>Quantity x unit price, formatted with currency</t>
+  </si>
+  <si>
+    <t>VAT recap</t>
+  </si>
+  <si>
+    <t>{{#taxLines}}</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per distinct tax rate</t>
   </si>
   <si>
     <t>{{taxLines.rate}}</t>
   </si>
   <si>
+    <t>Tax rate percentage (e.g. 19%)</t>
+  </si>
+  <si>
     <t>{{taxLines.base}}</t>
   </si>
   <si>
+    <t>Taxable base for this rate</t>
+  </si>
+  <si>
     <t>{{taxLines.amount}}</t>
-  </si>
-  <si>
-    <t>{{#taxLines}}</t>
-  </si>
-  <si>
-    <t>Total Brut HTVA</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.subTotal}}</t>
-  </si>
-  <si>
-    <t>Total TVA</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.taxTotal}}</t>
-  </si>
-  <si>
-    <t>Total TTC</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.total}}</t>
-  </si>
-  <si>
-    <t>Cachet et Signature</t>
-  </si>
-  <si>
-    <t>IBAN : {{organization.iban}}</t>
-  </si>
-  <si>
-    <t>{{organization.bankName}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Buyer logo — place alone in a cell to anchor the uploaded image there</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.number}}</t>
-  </si>
-  <si>
-    <t>Vendor's invoice number</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.date}}</t>
-  </si>
-  <si>
-    <t>Bill date</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.dueDate}}</t>
-  </si>
-  <si>
-    <t>Payment due date, blank if unset</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.reference}}</t>
-  </si>
-  <si>
-    <t>Free-text reference, blank if unset</t>
-  </si>
-  <si>
-    <t>{{incomingInvoice.purchaseOrder}}</t>
-  </si>
-  <si>
-    <t>Linked purchase order number, blank if unset</t>
-  </si>
-  <si>
-    <t>Buyer (bill recipient) company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Buyer VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Buyer email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Buyer phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Buyer website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Buyer street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Buyer house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Buyer postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Buyer city</t>
-  </si>
-  <si>
-    <t>{{organization.iban}}</t>
-  </si>
-  <si>
-    <t>Buyer IBAN</t>
-  </si>
-  <si>
-    <t>Buyer bank name</t>
-  </si>
-  <si>
-    <t>Vendor name</t>
-  </si>
-  <si>
-    <t>{{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>Vendor VAT number</t>
-  </si>
-  <si>
-    <t>{{vendor.email}}</t>
-  </si>
-  <si>
-    <t>Vendor email</t>
-  </si>
-  <si>
-    <t>{{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>Vendor phone</t>
-  </si>
-  <si>
-    <t>{{vendor.street}}</t>
-  </si>
-  <si>
-    <t>Vendor street</t>
-  </si>
-  <si>
-    <t>{{vendor.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Vendor house number</t>
-  </si>
-  <si>
-    <t>{{vendor.postalCode}}</t>
-  </si>
-  <si>
-    <t>Vendor postal code</t>
-  </si>
-  <si>
-    <t>{{vendor.city}}</t>
-  </si>
-  <si>
-    <t>Vendor city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Unit price, formatted with currency</t>
-  </si>
-  <si>
-    <t>{{lineItems.taxRate}}</t>
-  </si>
-  <si>
-    <t>Tax rate percentage (e.g. 19.5%), blank if unset</t>
-  </si>
-  <si>
-    <t>Quantity x unit price, formatted with currency</t>
-  </si>
-  <si>
-    <t>VAT recap</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in one cell of the row to repeat once per distinct tax rate</t>
-  </si>
-  <si>
-    <t>Tax rate percentage (e.g. 19%)</t>
-  </si>
-  <si>
-    <t>Taxable base for this rate</t>
   </si>
   <si>
     <t>VAT amount for this rate</t>
@@ -405,13 +402,13 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="14"/>
     </font>
     <font>
       <family val="2"/>
@@ -463,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -489,10 +486,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -774,194 +774,152 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="34"/>
-    <col customWidth="true" max="4" min="3" width="16"/>
+    <col customWidth="true" max="2" min="1" width="28"/>
+    <col customWidth="true" max="5" min="3" width="14"/>
+    <col customWidth="true" max="6" min="6" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>5</v>
+      <c r="A7" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="D13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="E13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="F13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J12" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
+    <row r="19">
+      <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="1" t="s">
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="D24" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:G28"/>
+  <mergeCells count="2">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -981,393 +939,393 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="s">
-        <v>92</v>
+      <c r="A32" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="s">
-        <v>100</v>
+      <c r="A39" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="C43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" t="s">
         <v>109</v>
       </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" t="s">
         <v>112</v>
-      </c>
-      <c r="C50" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
         <v>114</v>
-      </c>
-      <c r="C51" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" t="s">
         <v>116</v>
-      </c>
-      <c r="C52" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/db/templates/incoming_invoice_default.xlsx
+++ b/db/templates/incoming_invoice_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>{{vendor.name}}</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>Linked product's SKU (the Code column), blank on a free-text line</t>
   </si>
   <si>
     <t>Line item description</t>
@@ -1187,54 +1193,54 @@
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="s">
         <v>25</v>
       </c>
-      <c r="C38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="s">
-        <v>95</v>
+      <c r="C39" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="A40" s="12" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1263,52 +1269,52 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="s">
+      <c r="B44" t="s">
         <v>104</v>
       </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
+      <c r="A45" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="s">
+      <c r="B49" t="s">
         <v>110</v>
       </c>
+      <c r="C49" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="50">
-      <c r="B50" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="A50" s="12" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1326,6 +1332,14 @@
       </c>
       <c r="C52" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1333,9 +1347,9 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A50:C50"/>
   </mergeCells>
 </worksheet>
 </file>